--- a/sample-data/split/Students.xlsx
+++ b/sample-data/split/Students.xlsx
@@ -56,13 +56,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -429,22 +426,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>StudentId</t>
+          <t>StudentID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -464,353 +462,29 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>FatherName</t>
+          <t>ParentName</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>FatherEmail</t>
+          <t>ParentsEmailID</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>FatherPhone</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>S7001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Aarav Mehta</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Grade 7</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Rakesh Mehta</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>rakesh.mehta@example.com</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>9876543210</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>S9002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Isha Mehta</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Rakesh Mehta</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>rakesh.mehta@example.com</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>+91 98765 43210</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>S7003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Vivaan Shah</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>VII</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Nilesh Shah</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>nilesh.shah@example.com</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9812345678</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>S7004</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Diya Patel</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Grade 7</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Amit Patel</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9900112233</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>S7005</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Kabir Anand</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Grade 7</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Rohit Anand</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>rohit.anand@example.com</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9822334455</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>S9006</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Sara Rao</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Grade 9</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Sunil Rao</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>sunil.rao@example.com</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9765432109</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>S5007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Myra Joshi</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Class 5</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Paresh Joshi</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>paresh.joshi@example.com</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9700000001</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>S5008</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Aditya Nair</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Grade 5</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Manoj Nair</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>manoj.nair@example.com</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9700000002</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>S1009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Tara Iyer</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Grade 1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Suresh Iyer</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>suresh.iyer@example.com</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9700000003</t>
+          <t>FathersMobileNo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>MothersMobileNo</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Unrecognised grade" error="Pick a grade from the list. A different spelling makes the row disappear from the site." type="list">
-      <formula1>"JK,Grade 1,Grade 2,Grade 3,Grade 4,Grade 5,Grade 6,Grade 7,Grade 8,Grade 9,Grade 10,Grade 11,Grade 12"</formula1>
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Unrecognised grade" error="Pick a grade from the list. A different spelling makes the row disappear from the site." type="list">
+      <formula1>"JK,SK,Grade 1,Grade 2,Grade 3,Grade 4,Grade 5,Grade 6,Grade 7,Grade 8,Grade 9,Grade 10,Grade 11,Grade 12"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
